--- a/Team-Data/2012-13/3-18-2012-13.xlsx
+++ b/Team-Data/2012-13/3-18-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E2" t="n">
         <v>37</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>0.552</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J2" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K2" t="n">
-        <v>0.465</v>
+        <v>0.463</v>
       </c>
       <c r="L2" t="n">
         <v>8.9</v>
@@ -694,10 +761,10 @@
         <v>0.379</v>
       </c>
       <c r="O2" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="P2" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="Q2" t="n">
         <v>0.706</v>
@@ -706,13 +773,13 @@
         <v>9.300000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T2" t="n">
-        <v>40.7</v>
+        <v>40.9</v>
       </c>
       <c r="U2" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="V2" t="n">
         <v>15.1</v>
@@ -721,25 +788,25 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y2" t="n">
         <v>4.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -748,16 +815,16 @@
         <v>10</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
         <v>6</v>
@@ -766,7 +833,7 @@
         <v>3</v>
       </c>
       <c r="AM2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
         <v>5</v>
@@ -775,13 +842,13 @@
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ2" t="n">
         <v>26</v>
       </c>
       <c r="AR2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS2" t="n">
         <v>12</v>
@@ -793,13 +860,13 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY2" t="n">
         <v>6</v>
@@ -811,10 +878,10 @@
         <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" t="n">
         <v>36</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>0.545</v>
+        <v>0.554</v>
       </c>
       <c r="H3" t="n">
         <v>49.2</v>
@@ -861,43 +928,43 @@
         <v>36.9</v>
       </c>
       <c r="J3" t="n">
-        <v>80.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L3" t="n">
         <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="N3" t="n">
-        <v>0.357</v>
+        <v>0.354</v>
       </c>
       <c r="O3" t="n">
         <v>16.3</v>
       </c>
       <c r="P3" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.774</v>
+        <v>0.777</v>
       </c>
       <c r="R3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S3" t="n">
         <v>31.7</v>
       </c>
       <c r="T3" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="U3" t="n">
         <v>23.1</v>
       </c>
       <c r="V3" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W3" t="n">
         <v>8.4</v>
@@ -906,16 +973,16 @@
         <v>4.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AA3" t="n">
         <v>19.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC3" t="n">
         <v>0.4</v>
@@ -942,7 +1009,7 @@
         <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL3" t="n">
         <v>24</v>
@@ -951,22 +1018,22 @@
         <v>26</v>
       </c>
       <c r="AN3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO3" t="n">
         <v>21</v>
       </c>
       <c r="AP3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
         <v>29</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="n">
         <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.582</v>
+        <v>0.576</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J4" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.444</v>
+        <v>0.442</v>
       </c>
       <c r="L4" t="n">
         <v>7.8</v>
@@ -1055,7 +1122,7 @@
         <v>21.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.36</v>
+        <v>0.359</v>
       </c>
       <c r="O4" t="n">
         <v>17.3</v>
@@ -1064,13 +1131,13 @@
         <v>23.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.736</v>
+        <v>0.734</v>
       </c>
       <c r="R4" t="n">
         <v>12.5</v>
       </c>
       <c r="S4" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T4" t="n">
         <v>42.7</v>
@@ -1097,13 +1164,13 @@
         <v>21.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
         <v>8</v>
@@ -1115,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
@@ -1124,7 +1191,7 @@
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1133,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AO4" t="n">
         <v>12</v>
@@ -1145,25 +1212,25 @@
         <v>23</v>
       </c>
       <c r="AR4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU4" t="n">
         <v>28</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
         <v>23</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
         <v>12</v>
@@ -1178,7 +1245,7 @@
         <v>19</v>
       </c>
       <c r="BC4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -1207,61 +1274,61 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
         <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>0.224</v>
+        <v>0.212</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="J5" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0.419</v>
+        <v>0.417</v>
       </c>
       <c r="L5" t="n">
         <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.339</v>
+        <v>0.338</v>
       </c>
       <c r="O5" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P5" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q5" t="n">
         <v>0.746</v>
       </c>
       <c r="R5" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S5" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="T5" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="U5" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="V5" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W5" t="n">
         <v>7.2</v>
@@ -1270,22 +1337,22 @@
         <v>6</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="Z5" t="n">
         <v>19.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.09999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-9.9</v>
+        <v>-10.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1297,13 +1364,13 @@
         <v>30</v>
       </c>
       <c r="AH5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI5" t="n">
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1318,22 +1385,22 @@
         <v>27</v>
       </c>
       <c r="AO5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP5" t="n">
         <v>4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR5" t="n">
         <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU5" t="n">
         <v>30</v>
@@ -1351,7 +1418,7 @@
         <v>30</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -1389,25 +1456,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E6" t="n">
         <v>36</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>0.545</v>
+        <v>0.554</v>
       </c>
       <c r="H6" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I6" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J6" t="n">
-        <v>81.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0.435</v>
@@ -1416,10 +1483,10 @@
         <v>4.9</v>
       </c>
       <c r="M6" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.34</v>
+        <v>0.339</v>
       </c>
       <c r="O6" t="n">
         <v>16.8</v>
@@ -1428,7 +1495,7 @@
         <v>21.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.788</v>
+        <v>0.787</v>
       </c>
       <c r="R6" t="n">
         <v>12.8</v>
@@ -1440,7 +1507,7 @@
         <v>43.4</v>
       </c>
       <c r="U6" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V6" t="n">
         <v>14.7</v>
@@ -1449,7 +1516,7 @@
         <v>7.3</v>
       </c>
       <c r="X6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y6" t="n">
         <v>5.9</v>
@@ -1461,7 +1528,7 @@
         <v>19.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>0.5</v>
@@ -1479,16 +1546,16 @@
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1512,22 +1579,22 @@
         <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
         <v>19</v>
       </c>
       <c r="AX6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY6" t="n">
         <v>22</v>
@@ -1539,10 +1606,10 @@
         <v>16</v>
       </c>
       <c r="BB6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -1571,55 +1638,55 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" t="n">
         <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>0.328</v>
+        <v>0.333</v>
       </c>
       <c r="H7" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I7" t="n">
         <v>36.5</v>
       </c>
       <c r="J7" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K7" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L7" t="n">
         <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="O7" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P7" t="n">
         <v>23.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R7" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S7" t="n">
         <v>28.3</v>
       </c>
       <c r="T7" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U7" t="n">
         <v>20.6</v>
@@ -1631,7 +1698,7 @@
         <v>8.1</v>
       </c>
       <c r="X7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y7" t="n">
         <v>7.1</v>
@@ -1643,22 +1710,22 @@
         <v>20.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>97.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>-3.8</v>
+        <v>-3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH7" t="n">
         <v>27</v>
@@ -1670,7 +1737,7 @@
         <v>4</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL7" t="n">
         <v>16</v>
@@ -1679,7 +1746,7 @@
         <v>13</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
         <v>11</v>
@@ -1691,7 +1758,7 @@
         <v>16</v>
       </c>
       <c r="AR7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
         <v>30</v>
@@ -1700,7 +1767,7 @@
         <v>25</v>
       </c>
       <c r="AU7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV7" t="n">
         <v>6</v>
@@ -1721,10 +1788,10 @@
         <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -1753,46 +1820,46 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8" t="n">
         <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>0.478</v>
+        <v>0.47</v>
       </c>
       <c r="H8" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I8" t="n">
-        <v>38.7</v>
+        <v>38.5</v>
       </c>
       <c r="J8" t="n">
         <v>84.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0.46</v>
+        <v>0.458</v>
       </c>
       <c r="L8" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M8" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.375</v>
+        <v>0.372</v>
       </c>
       <c r="O8" t="n">
         <v>16.6</v>
       </c>
       <c r="P8" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.795</v>
+        <v>0.794</v>
       </c>
       <c r="R8" t="n">
         <v>9.300000000000001</v>
@@ -1801,10 +1868,10 @@
         <v>32.8</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U8" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="V8" t="n">
         <v>14.2</v>
@@ -1813,34 +1880,34 @@
         <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>101.5</v>
+        <v>101.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
         <v>18</v>
       </c>
       <c r="AF8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
@@ -1852,16 +1919,16 @@
         <v>3</v>
       </c>
       <c r="AK8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
         <v>17</v>
@@ -1873,7 +1940,7 @@
         <v>2</v>
       </c>
       <c r="AR8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS8" t="n">
         <v>6</v>
@@ -1891,10 +1958,10 @@
         <v>17</v>
       </c>
       <c r="AX8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ8" t="n">
         <v>24</v>
@@ -1906,7 +1973,7 @@
         <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F9" t="n">
         <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>0.676</v>
+        <v>0.672</v>
       </c>
       <c r="H9" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I9" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="J9" t="n">
-        <v>85.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.478</v>
+        <v>0.479</v>
       </c>
       <c r="L9" t="n">
         <v>6.5</v>
@@ -1974,16 +2041,16 @@
         <v>25.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="S9" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T9" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
       <c r="U9" t="n">
         <v>24.4</v>
@@ -2007,7 +2074,7 @@
         <v>21.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>106</v>
+        <v>105.8</v>
       </c>
       <c r="AC9" t="n">
         <v>4.9</v>
@@ -2016,7 +2083,7 @@
         <v>4</v>
       </c>
       <c r="AE9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF9" t="n">
         <v>6</v>
@@ -2025,7 +2092,7 @@
         <v>6</v>
       </c>
       <c r="AH9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -2117,22 +2184,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>0.333</v>
+        <v>0.338</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J10" t="n">
         <v>81.3</v>
@@ -2147,25 +2214,25 @@
         <v>17.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0.356</v>
+        <v>0.361</v>
       </c>
       <c r="O10" t="n">
         <v>15.9</v>
       </c>
       <c r="P10" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.695</v>
+        <v>0.694</v>
       </c>
       <c r="R10" t="n">
         <v>12.2</v>
       </c>
       <c r="S10" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="T10" t="n">
-        <v>42.4</v>
+        <v>42.6</v>
       </c>
       <c r="U10" t="n">
         <v>20.9</v>
@@ -2183,16 +2250,16 @@
         <v>5.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>94.3</v>
+        <v>94.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4.6</v>
+        <v>-4.1</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
@@ -2201,13 +2268,13 @@
         <v>22</v>
       </c>
       <c r="AF10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
         <v>23</v>
@@ -2225,13 +2292,13 @@
         <v>25</v>
       </c>
       <c r="AN10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AO10" t="n">
         <v>24</v>
       </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ10" t="n">
         <v>28</v>
@@ -2243,7 +2310,7 @@
         <v>17</v>
       </c>
       <c r="AT10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AU10" t="n">
         <v>24</v>
@@ -2267,7 +2334,7 @@
         <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC10" t="n">
         <v>26</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -2299,49 +2366,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11" t="n">
         <v>30</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J11" t="n">
-        <v>83</v>
+        <v>83.2</v>
       </c>
       <c r="K11" t="n">
         <v>0.454</v>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M11" t="n">
         <v>19.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4</v>
+        <v>0.398</v>
       </c>
       <c r="O11" t="n">
         <v>17.2</v>
       </c>
       <c r="P11" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.792</v>
+        <v>0.791</v>
       </c>
       <c r="R11" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S11" t="n">
         <v>34.1</v>
@@ -2359,7 +2426,7 @@
         <v>6.8</v>
       </c>
       <c r="X11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y11" t="n">
         <v>5</v>
@@ -2368,13 +2435,13 @@
         <v>21.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>100.6</v>
+        <v>100.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="AD11" t="n">
         <v>1</v>
@@ -2383,13 +2450,13 @@
         <v>8</v>
       </c>
       <c r="AF11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>10</v>
@@ -2419,7 +2486,7 @@
         <v>3</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
@@ -2428,7 +2495,7 @@
         <v>3</v>
       </c>
       <c r="AU11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV11" t="n">
         <v>25</v>
@@ -2437,13 +2504,13 @@
         <v>27</v>
       </c>
       <c r="AX11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA11" t="n">
         <v>20</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
         <v>12</v>
@@ -2586,10 +2653,10 @@
         <v>1</v>
       </c>
       <c r="AM12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2601,7 +2668,7 @@
         <v>17</v>
       </c>
       <c r="AR12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -2663,25 +2730,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F13" t="n">
         <v>26</v>
       </c>
       <c r="G13" t="n">
-        <v>0.612</v>
+        <v>0.606</v>
       </c>
       <c r="H13" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I13" t="n">
         <v>35.1</v>
       </c>
       <c r="J13" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K13" t="n">
         <v>0.434</v>
@@ -2696,31 +2763,31 @@
         <v>0.358</v>
       </c>
       <c r="O13" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="P13" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.747</v>
+        <v>0.745</v>
       </c>
       <c r="R13" t="n">
         <v>12.9</v>
       </c>
       <c r="S13" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="T13" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="U13" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V13" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W13" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X13" t="n">
         <v>6.6</v>
@@ -2729,19 +2796,19 @@
         <v>5.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2759,7 +2826,7 @@
         <v>29</v>
       </c>
       <c r="AJ13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
         <v>28</v>
@@ -2774,13 +2841,13 @@
         <v>17</v>
       </c>
       <c r="AO13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP13" t="n">
         <v>14</v>
       </c>
-      <c r="AP13" t="n">
-        <v>13</v>
-      </c>
       <c r="AQ13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR13" t="n">
         <v>3</v>
@@ -2795,7 +2862,7 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW13" t="n">
         <v>25</v>
@@ -2813,7 +2880,7 @@
         <v>4</v>
       </c>
       <c r="BB13" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BC13" t="n">
         <v>6</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
         <v>4</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO14" t="n">
         <v>18</v>
@@ -2968,16 +3035,16 @@
         <v>15</v>
       </c>
       <c r="AS14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E15" t="n">
         <v>36</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>0.522</v>
+        <v>0.529</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.458</v>
+        <v>0.46</v>
       </c>
       <c r="L15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M15" t="n">
         <v>24.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O15" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S15" t="n">
         <v>33.2</v>
       </c>
       <c r="T15" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U15" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V15" t="n">
         <v>15.1</v>
@@ -3087,22 +3154,22 @@
         <v>7.1</v>
       </c>
       <c r="X15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y15" t="n">
         <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.1</v>
+        <v>102.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AD15" t="n">
         <v>1</v>
@@ -3111,7 +3178,7 @@
         <v>12</v>
       </c>
       <c r="AF15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
         <v>15</v>
@@ -3120,13 +3187,13 @@
         <v>28</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AJ15" t="n">
         <v>22</v>
       </c>
       <c r="AK15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL15" t="n">
         <v>4</v>
@@ -3135,10 +3202,10 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
@@ -3156,16 +3223,16 @@
         <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW15" t="n">
         <v>24</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
         <v>16</v>
@@ -3180,7 +3247,7 @@
         <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -3209,82 +3276,82 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E16" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F16" t="n">
         <v>21</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.677</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J16" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L16" t="n">
         <v>4.7</v>
       </c>
       <c r="M16" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O16" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P16" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.772</v>
+        <v>0.774</v>
       </c>
       <c r="R16" t="n">
         <v>13.2</v>
       </c>
       <c r="S16" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T16" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U16" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V16" t="n">
         <v>14.4</v>
       </c>
       <c r="W16" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z16" t="n">
         <v>20</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB16" t="n">
         <v>93.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD16" t="n">
         <v>21</v>
@@ -3299,10 +3366,10 @@
         <v>5</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AJ16" t="n">
         <v>13</v>
@@ -3317,16 +3384,16 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP16" t="n">
         <v>24</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
         <v>2</v>
@@ -3335,19 +3402,19 @@
         <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV16" t="n">
         <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
@@ -3356,7 +3423,7 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB16" t="n">
         <v>26</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.788</v>
+        <v>0.785</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
@@ -3409,7 +3476,7 @@
         <v>38.9</v>
       </c>
       <c r="J17" t="n">
-        <v>78.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="K17" t="n">
         <v>0.496</v>
@@ -3424,13 +3491,13 @@
         <v>0.386</v>
       </c>
       <c r="O17" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P17" t="n">
         <v>23</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="R17" t="n">
         <v>8.4</v>
@@ -3451,19 +3518,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>103.5</v>
+        <v>103.4</v>
       </c>
       <c r="AC17" t="n">
         <v>7.6</v>
@@ -3502,7 +3569,7 @@
         <v>3</v>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -3514,22 +3581,22 @@
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW17" t="n">
         <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-1.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>17</v>
@@ -3660,7 +3727,7 @@
         <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH18" t="n">
         <v>14</v>
@@ -3684,7 +3751,7 @@
         <v>16</v>
       </c>
       <c r="AO18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP18" t="n">
         <v>18</v>
@@ -3702,7 +3769,7 @@
         <v>5</v>
       </c>
       <c r="AU18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV18" t="n">
         <v>8</v>
@@ -3717,10 +3784,10 @@
         <v>8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB18" t="n">
         <v>11</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" t="n">
         <v>23</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G19" t="n">
-        <v>0.354</v>
+        <v>0.359</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J19" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.434</v>
+        <v>0.436</v>
       </c>
       <c r="L19" t="n">
         <v>5.4</v>
@@ -3785,13 +3852,13 @@
         <v>18</v>
       </c>
       <c r="N19" t="n">
-        <v>0.298</v>
+        <v>0.299</v>
       </c>
       <c r="O19" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P19" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q19" t="n">
         <v>0.73</v>
@@ -3806,40 +3873,40 @@
         <v>42.6</v>
       </c>
       <c r="U19" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V19" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W19" t="n">
         <v>8.1</v>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA19" t="n">
         <v>22.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>94.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE19" t="n">
         <v>22</v>
       </c>
       <c r="AF19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
         <v>22</v>
@@ -3848,13 +3915,13 @@
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK19" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>28</v>
@@ -3875,28 +3942,28 @@
         <v>24</v>
       </c>
       <c r="AR19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS19" t="n">
         <v>18</v>
       </c>
       <c r="AT19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU19" t="n">
         <v>18</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW19" t="n">
         <v>13</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ19" t="n">
         <v>5</v>
@@ -3905,7 +3972,7 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BC19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -3937,46 +4004,46 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G20" t="n">
-        <v>0.324</v>
+        <v>0.328</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J20" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.45</v>
+        <v>0.452</v>
       </c>
       <c r="L20" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M20" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.365</v>
+        <v>0.368</v>
       </c>
       <c r="O20" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="P20" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.774</v>
+        <v>0.772</v>
       </c>
       <c r="R20" t="n">
         <v>11.6</v>
@@ -3988,13 +4055,13 @@
         <v>41.2</v>
       </c>
       <c r="U20" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V20" t="n">
         <v>14.3</v>
       </c>
       <c r="W20" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="X20" t="n">
         <v>5.5</v>
@@ -4003,34 +4070,34 @@
         <v>6.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA20" t="n">
         <v>18.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>94</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.9</v>
+        <v>-3.6</v>
       </c>
       <c r="AD20" t="n">
         <v>4</v>
       </c>
       <c r="AE20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG20" t="n">
         <v>27</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>28</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ20" t="n">
         <v>25</v>
@@ -4045,16 +4112,16 @@
         <v>21</v>
       </c>
       <c r="AN20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO20" t="n">
         <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
         <v>11</v>
@@ -4066,7 +4133,7 @@
         <v>21</v>
       </c>
       <c r="AU20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV20" t="n">
         <v>9</v>
@@ -4087,10 +4154,10 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E21" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F21" t="n">
         <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6</v>
+        <v>0.594</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J21" t="n">
-        <v>81.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="K21" t="n">
         <v>0.439</v>
@@ -4146,31 +4213,31 @@
         <v>10.7</v>
       </c>
       <c r="M21" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="O21" t="n">
         <v>16.4</v>
       </c>
       <c r="P21" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Q21" t="n">
         <v>0.758</v>
       </c>
       <c r="R21" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S21" t="n">
         <v>30</v>
       </c>
       <c r="T21" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U21" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="V21" t="n">
         <v>12.2</v>
@@ -4188,16 +4255,16 @@
         <v>19.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="AC21" t="n">
         <v>2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
@@ -4215,7 +4282,7 @@
         <v>24</v>
       </c>
       <c r="AJ21" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AK21" t="n">
         <v>23</v>
@@ -4224,13 +4291,13 @@
         <v>2</v>
       </c>
       <c r="AM21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP21" t="n">
         <v>17</v>
@@ -4245,7 +4312,7 @@
         <v>23</v>
       </c>
       <c r="AT21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU21" t="n">
         <v>29</v>
@@ -4260,7 +4327,7 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ21" t="n">
         <v>13</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4403,7 +4470,7 @@
         <v>3</v>
       </c>
       <c r="AL22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM22" t="n">
         <v>17</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-6.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4585,7 +4652,7 @@
         <v>12</v>
       </c>
       <c r="AL23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="n">
         <v>16</v>
@@ -4606,7 +4673,7 @@
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT23" t="n">
         <v>15</v>
@@ -4621,7 +4688,7 @@
         <v>30</v>
       </c>
       <c r="AX23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -4665,58 +4732,58 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" t="n">
         <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>0.394</v>
+        <v>0.385</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J24" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L24" t="n">
         <v>6.2</v>
       </c>
       <c r="M24" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O24" t="n">
         <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.718</v>
+        <v>0.717</v>
       </c>
       <c r="R24" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S24" t="n">
         <v>30.6</v>
       </c>
       <c r="T24" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U24" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V24" t="n">
         <v>13</v>
@@ -4731,40 +4798,40 @@
         <v>4.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.6</v>
+        <v>-3.7</v>
       </c>
       <c r="AD24" t="n">
         <v>21</v>
       </c>
       <c r="AE24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF24" t="n">
         <v>20</v>
       </c>
       <c r="AG24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH24" t="n">
         <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ24" t="n">
         <v>7</v>
       </c>
       <c r="AK24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
@@ -4788,7 +4855,7 @@
         <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT24" t="n">
         <v>20</v>
@@ -4815,10 +4882,10 @@
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -4847,28 +4914,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F25" t="n">
         <v>45</v>
       </c>
       <c r="G25" t="n">
-        <v>0.338</v>
+        <v>0.328</v>
       </c>
       <c r="H25" t="n">
         <v>48.4</v>
       </c>
       <c r="I25" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J25" t="n">
         <v>84</v>
       </c>
       <c r="K25" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L25" t="n">
         <v>5.7</v>
@@ -4877,25 +4944,25 @@
         <v>17.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.325</v>
+        <v>0.324</v>
       </c>
       <c r="O25" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="P25" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.737</v>
+        <v>0.74</v>
       </c>
       <c r="R25" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S25" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="T25" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="U25" t="n">
         <v>22.2</v>
@@ -4907,37 +4974,37 @@
         <v>8</v>
       </c>
       <c r="X25" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AB25" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>-5.9</v>
+        <v>-6.3</v>
       </c>
       <c r="AD25" t="n">
         <v>4</v>
       </c>
       <c r="AE25" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AF25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AH25" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI25" t="n">
         <v>15</v>
@@ -4946,7 +5013,7 @@
         <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL25" t="n">
         <v>27</v>
@@ -4964,13 +5031,13 @@
         <v>26</v>
       </c>
       <c r="AQ25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS25" t="n">
         <v>22</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>19</v>
       </c>
       <c r="AT25" t="n">
         <v>17</v>
@@ -4982,22 +5049,22 @@
         <v>28</v>
       </c>
       <c r="AW25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA25" t="n">
         <v>27</v>
       </c>
       <c r="BB25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BC25" t="n">
         <v>28</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E26" t="n">
         <v>31</v>
       </c>
       <c r="F26" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G26" t="n">
-        <v>0.47</v>
+        <v>0.477</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J26" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K26" t="n">
         <v>0.449</v>
@@ -5059,13 +5126,13 @@
         <v>23.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="O26" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P26" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q26" t="n">
         <v>0.781</v>
@@ -5074,13 +5141,13 @@
         <v>11.1</v>
       </c>
       <c r="S26" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T26" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U26" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V26" t="n">
         <v>14.7</v>
@@ -5104,22 +5171,22 @@
         <v>98.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="AD26" t="n">
         <v>21</v>
       </c>
       <c r="AE26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF26" t="n">
         <v>18</v>
       </c>
       <c r="AG26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI26" t="n">
         <v>17</v>
@@ -5134,16 +5201,16 @@
         <v>6</v>
       </c>
       <c r="AM26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
         <v>22</v>
       </c>
       <c r="AO26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ26" t="n">
         <v>7</v>
@@ -5155,7 +5222,7 @@
         <v>16</v>
       </c>
       <c r="AT26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU26" t="n">
         <v>21</v>
@@ -5167,16 +5234,16 @@
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
         <v>6</v>
       </c>
       <c r="BA26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB26" t="n">
         <v>13</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-5.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
@@ -5301,10 +5368,10 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ27" t="n">
         <v>6</v>
@@ -5319,22 +5386,22 @@
         <v>15</v>
       </c>
       <c r="AN27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO27" t="n">
         <v>8</v>
       </c>
       <c r="AP27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ27" t="n">
         <v>12</v>
       </c>
       <c r="AR27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT27" t="n">
         <v>26</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -5471,10 +5538,10 @@
         <v>8</v>
       </c>
       <c r="AD28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="n">
         <v>2</v>
@@ -5483,7 +5550,7 @@
         <v>2</v>
       </c>
       <c r="AH28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
@@ -5504,7 +5571,7 @@
         <v>4</v>
       </c>
       <c r="AO28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP28" t="n">
         <v>19</v>
@@ -5519,7 +5586,7 @@
         <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5528,10 +5595,10 @@
         <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
@@ -5540,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
@@ -5662,7 +5729,7 @@
         <v>21</v>
       </c>
       <c r="AG29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
@@ -5674,7 +5741,7 @@
         <v>11</v>
       </c>
       <c r="AK29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="n">
         <v>14</v>
@@ -5683,10 +5750,10 @@
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -5701,13 +5768,13 @@
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU29" t="n">
         <v>20</v>
       </c>
       <c r="AV29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW29" t="n">
         <v>18</v>
@@ -5725,7 +5792,7 @@
         <v>15</v>
       </c>
       <c r="BB29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC29" t="n">
         <v>20</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -5757,37 +5824,37 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E30" t="n">
         <v>34</v>
       </c>
       <c r="F30" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G30" t="n">
-        <v>0.507</v>
+        <v>0.515</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J30" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L30" t="n">
         <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.36</v>
+        <v>0.358</v>
       </c>
       <c r="O30" t="n">
         <v>18.5</v>
@@ -5796,19 +5863,19 @@
         <v>24.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="R30" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S30" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T30" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U30" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="V30" t="n">
         <v>15</v>
@@ -5817,37 +5884,37 @@
         <v>8.199999999999999</v>
       </c>
       <c r="X30" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="AA30" t="n">
         <v>20.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>97.90000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.7</v>
+        <v>-0.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
       </c>
       <c r="AF30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG30" t="n">
         <v>16</v>
       </c>
-      <c r="AG30" t="n">
-        <v>17</v>
-      </c>
       <c r="AH30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI30" t="n">
         <v>18</v>
@@ -5865,7 +5932,7 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AO30" t="n">
         <v>5</v>
@@ -5877,16 +5944,16 @@
         <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS30" t="n">
         <v>24</v>
       </c>
       <c r="AT30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU30" t="n">
         <v>13</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>14</v>
       </c>
       <c r="AV30" t="n">
         <v>20</v>
@@ -5898,10 +5965,10 @@
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA30" t="n">
         <v>9</v>
@@ -5910,7 +5977,7 @@
         <v>14</v>
       </c>
       <c r="BC30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E31" t="n">
         <v>23</v>
       </c>
       <c r="F31" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G31" t="n">
-        <v>0.348</v>
+        <v>0.354</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J31" t="n">
         <v>81.8</v>
       </c>
       <c r="K31" t="n">
-        <v>0.435</v>
+        <v>0.433</v>
       </c>
       <c r="L31" t="n">
         <v>6.7</v>
@@ -5972,19 +6039,19 @@
         <v>0.364</v>
       </c>
       <c r="O31" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="P31" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.738</v>
+        <v>0.737</v>
       </c>
       <c r="R31" t="n">
         <v>10.8</v>
       </c>
       <c r="S31" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T31" t="n">
         <v>43.4</v>
@@ -5996,7 +6063,7 @@
         <v>15.4</v>
       </c>
       <c r="W31" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X31" t="n">
         <v>4.7</v>
@@ -6005,16 +6072,16 @@
         <v>4.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA31" t="n">
         <v>18.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>92.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AD31" t="n">
         <v>21</v>
@@ -6029,16 +6096,16 @@
         <v>23</v>
       </c>
       <c r="AH31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK31" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AL31" t="n">
         <v>18</v>
@@ -6056,10 +6123,10 @@
         <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS31" t="n">
         <v>7</v>
@@ -6068,7 +6135,7 @@
         <v>6</v>
       </c>
       <c r="AU31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV31" t="n">
         <v>27</v>
@@ -6083,7 +6150,7 @@
         <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA31" t="n">
         <v>25</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-18-2012-13</t>
+          <t>2013-03-18</t>
         </is>
       </c>
     </row>
